--- a/data/trans_dic/IQ23_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que duermen las horas recomendadas en función de su edad</t>
+          <t>Menores que duermen las horas recomendadas en función de su edad (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,58; 82,95</t>
+          <t>70,13; 83,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,86; 84,52</t>
+          <t>69,93; 84,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,51; 65,71</t>
+          <t>47,45; 65,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63,5; 78,05</t>
+          <t>63,25; 77,47</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>67,1; 81,31</t>
+          <t>66,23; 81,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,85; 75,87</t>
+          <t>58,94; 75,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,1; 74,89</t>
+          <t>59,59; 74,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>67,82; 81,48</t>
+          <t>67,31; 82,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>70,75; 80,29</t>
+          <t>70,46; 80,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67,84; 77,98</t>
+          <t>68,26; 78,09</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56,61; 68,48</t>
+          <t>56,94; 68,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,19; 78,18</t>
+          <t>68,15; 78,03</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>67,49; 81,73</t>
+          <t>66,93; 82,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,58; 82,49</t>
+          <t>67,95; 82,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,93; 80,76</t>
+          <t>66,85; 80,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63,52; 79,08</t>
+          <t>63,9; 78,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>63,93; 79,64</t>
+          <t>64,79; 80,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,15; 81,75</t>
+          <t>67,44; 81,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,68; 73,39</t>
+          <t>58,86; 73,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>68,07; 83,0</t>
+          <t>69,02; 83,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,31; 78,74</t>
+          <t>68,12; 79,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70,56; 80,24</t>
+          <t>70,01; 80,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,52; 75,29</t>
+          <t>64,74; 74,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>68,09; 78,37</t>
+          <t>68,37; 78,68</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,48; 78,43</t>
+          <t>60,26; 78,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,37; 77,58</t>
+          <t>60,94; 76,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,81; 76,71</t>
+          <t>57,96; 77,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,5; 82,91</t>
+          <t>61,93; 82,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,7; 81,21</t>
+          <t>66,89; 81,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64,36; 80,43</t>
+          <t>65,44; 80,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,79; 77,76</t>
+          <t>60,01; 77,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56,26; 76,27</t>
+          <t>55,66; 76,95</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66,88; 77,72</t>
+          <t>66,52; 78,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65,83; 76,65</t>
+          <t>65,18; 76,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62,11; 75,0</t>
+          <t>62,19; 75,34</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>62,9; 76,89</t>
+          <t>61,9; 76,81</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,15; 76,52</t>
+          <t>66,34; 76,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,48; 74,25</t>
+          <t>63,54; 74,02</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,27; 71,59</t>
+          <t>61,24; 71,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64,62; 81,72</t>
+          <t>64,17; 81,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,32; 79,64</t>
+          <t>70,32; 80,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,11; 75,23</t>
+          <t>64,76; 75,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,89; 69,3</t>
+          <t>58,44; 69,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,47; 71,0</t>
+          <t>58,46; 71,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,76; 77,05</t>
+          <t>70,05; 77,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65,56; 72,96</t>
+          <t>65,86; 73,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61,65; 69,31</t>
+          <t>61,47; 68,72</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,28; 74,66</t>
+          <t>63,45; 74,78</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>64,72; 78,69</t>
+          <t>64,56; 78,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64,83; 77,18</t>
+          <t>64,88; 77,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66,56; 78,9</t>
+          <t>67,32; 79,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60,68; 76,31</t>
+          <t>60,53; 76,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>69,02; 80,62</t>
+          <t>68,78; 81,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,34; 72,27</t>
+          <t>59,25; 72,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,73; 74,44</t>
+          <t>61,39; 74,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62,87; 77,59</t>
+          <t>62,89; 77,86</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68,45; 77,51</t>
+          <t>68,33; 78,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64,33; 73,32</t>
+          <t>64,66; 73,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66,02; 74,99</t>
+          <t>65,85; 75,04</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>64,26; 75,71</t>
+          <t>64,76; 75,03</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70,56; 86,15</t>
+          <t>71,41; 86,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>63,35; 83,13</t>
+          <t>63,97; 83,05</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61,63; 80,58</t>
+          <t>61,3; 80,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>63,58; 81,64</t>
+          <t>65,23; 82,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60,25; 77,59</t>
+          <t>61,32; 78,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,77; 88,21</t>
+          <t>73,65; 88,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,17; 72,21</t>
+          <t>53,77; 73,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55,9; 75,27</t>
+          <t>55,85; 76,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>69,31; 80,17</t>
+          <t>68,43; 80,16</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72,05; 83,65</t>
+          <t>72,08; 83,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>60,43; 73,57</t>
+          <t>60,7; 74,01</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>64,34; 76,43</t>
+          <t>63,64; 77,04</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>70,76; 76,35</t>
+          <t>71,1; 76,68</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69,44; 74,91</t>
+          <t>69,45; 74,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65,45; 71,31</t>
+          <t>65,36; 71,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67,99; 75,78</t>
+          <t>67,72; 75,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,59; 77,15</t>
+          <t>71,41; 76,84</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,37; 73,9</t>
+          <t>68,77; 74,6</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,1; 69,05</t>
+          <t>63,36; 69,29</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>66,46; 73,29</t>
+          <t>66,6; 73,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>72,03; 75,77</t>
+          <t>71,97; 75,79</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69,71; 74,02</t>
+          <t>69,92; 73,75</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65,29; 69,55</t>
+          <t>65,04; 69,44</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,35; 73,51</t>
+          <t>68,02; 72,86</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que duermen las horas recomendadas en función de su edad (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>79537</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>70419</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>46845</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>73700</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>72752</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>61106</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>67584</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>101442</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>152290</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>131525</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>114429</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>175143</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>72869; 86876</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62894; 76033</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>38828; 53460</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>65613; 80367</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>64600; 79145</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>52907; 67473</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>59468; 74586</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>91069; 110957</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>141944; 161931</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>122661; 140332</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>103414; 124282</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>162914; 186526</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>65030</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>70506</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>77200</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>67473</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>61610</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>72933</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>73714</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>72994</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>126640</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>143439</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>150914</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>140468</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>57976; 71121</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>63378; 76850</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>69915; 84185</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>60502; 74599</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>54935; 68234</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>65272; 78905</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>65257; 81553</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>65962; 80159</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>116760; 135568</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>133044; 152756</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>139484; 160634</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>130072; 149698</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>47152</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>60146</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>41978</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>37934</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>73563</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>63004</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>50815</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>42846</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>120716</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>123150</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>92794</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>80780</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>40610; 52763</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52505; 66051</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>35843; 47695</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>32119; 42632</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>65988; 80391</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>56420; 69282</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>43810; 56691</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>35540; 49132</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>110456; 129781</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>112364; 132248</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>83862; 101589</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>71626; 88883</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>432</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>412</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>141910</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>141316</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>147620</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>154205</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>152091</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>159805</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>133663</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>142094</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>294001</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>301121</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>281283</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>296299</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>131300; 151578</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>130035; 151482</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>135670; 158607</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>138932; 177247</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>142095; 162203</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>147287; 171914</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>121873; 144844</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>127373; 155457</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>280199; 308500</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>284572; 316139</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>264364; 295572</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>275631; 324848</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>279</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>74371</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>106658</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>99183</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>81460</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>94688</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93649</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>97581</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>114445</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>169059</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>200307</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>196766</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>195906</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>66823; 80915</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>96781; 115484</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>91221; 107372</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>71024; 89730</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>86618; 102390</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>83578; 101715</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>87845; 106149</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>102272; 126619</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>156785; 179049</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>187659; 212802</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>183449; 209062</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>181298; 210067</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>58683</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>39776</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>43927</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>50081</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>50652</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>60358</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>42999</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>48118</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>109336</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>100134</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>86926</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>98199</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>52918; 64078</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>34484; 44772</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>37444; 49290</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>44042; 55365</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>44387; 56659</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>54527; 65579</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>36471; 49673</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>40210; 54847</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>100238; 117425</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>92226; 106883</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>78250; 95412</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>88794; 107488</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>1347</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1265</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>466684</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>488821</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>456753</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>464855</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>505358</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>510855</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>466358</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>521940</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>972042</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>999677</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>923110</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>986795</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>450372; 485710</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>470260; 507746</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>435548; 476522</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>441280; 492589</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>486578; 523604</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>491903; 533598</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>445535; 487235</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>497648; 545864</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>946327; 996460</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>973533; 1026898</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>890706; 951022</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>951507; 1019196</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IQ23_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>70,13; 83,61</t>
+          <t>69,13; 82,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>69,93; 84,54</t>
+          <t>70,56; 84,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>47,45; 65,33</t>
+          <t>48,08; 66,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63,25; 77,47</t>
+          <t>62,96; 78,03</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>66,23; 81,14</t>
+          <t>67,21; 81,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,94; 75,17</t>
+          <t>59,43; 75,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,59; 74,74</t>
+          <t>60,2; 75,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>67,31; 82,0</t>
+          <t>67,21; 81,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>70,46; 80,38</t>
+          <t>70,27; 79,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68,26; 78,09</t>
+          <t>67,47; 77,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56,94; 68,43</t>
+          <t>57,36; 69,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,15; 78,03</t>
+          <t>67,97; 77,88</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,93; 82,11</t>
+          <t>66,37; 81,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,95; 82,4</t>
+          <t>67,5; 83,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,85; 80,5</t>
+          <t>67,37; 80,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63,9; 78,79</t>
+          <t>62,99; 78,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,79; 80,47</t>
+          <t>64,56; 80,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,44; 81,53</t>
+          <t>67,11; 81,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,86; 73,56</t>
+          <t>58,88; 73,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>69,02; 83,87</t>
+          <t>68,07; 83,41</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,12; 79,09</t>
+          <t>68,62; 79,0</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70,01; 80,38</t>
+          <t>70,48; 80,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,74; 74,56</t>
+          <t>64,93; 74,87</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>68,37; 78,68</t>
+          <t>67,78; 78,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,26; 78,29</t>
+          <t>59,41; 78,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,94; 76,66</t>
+          <t>60,74; 77,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>57,96; 77,13</t>
+          <t>58,89; 76,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,93; 82,2</t>
+          <t>61,49; 82,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>66,89; 81,5</t>
+          <t>67,01; 81,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65,44; 80,35</t>
+          <t>63,92; 79,79</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,01; 77,66</t>
+          <t>60,28; 77,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>55,66; 76,95</t>
+          <t>55,31; 76,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66,52; 78,16</t>
+          <t>67,18; 78,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65,18; 76,72</t>
+          <t>66,07; 76,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62,19; 75,34</t>
+          <t>63,05; 75,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>61,9; 76,81</t>
+          <t>60,47; 76,66</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,34; 76,59</t>
+          <t>66,27; 76,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,54; 74,02</t>
+          <t>63,48; 73,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,24; 71,59</t>
+          <t>61,6; 71,64</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>64,17; 81,87</t>
+          <t>63,94; 81,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,32; 80,27</t>
+          <t>70,47; 79,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,76; 75,59</t>
+          <t>64,89; 75,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,44; 69,45</t>
+          <t>58,5; 69,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,46; 71,35</t>
+          <t>58,95; 71,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>70,05; 77,13</t>
+          <t>69,68; 77,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65,86; 73,17</t>
+          <t>65,97; 73,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61,47; 68,72</t>
+          <t>61,21; 68,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,45; 74,78</t>
+          <t>63,15; 74,59</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>64,56; 78,18</t>
+          <t>64,76; 78,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64,88; 77,42</t>
+          <t>64,89; 77,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67,32; 79,24</t>
+          <t>66,79; 79,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60,53; 76,47</t>
+          <t>60,69; 76,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>68,78; 81,31</t>
+          <t>69,1; 81,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,25; 72,11</t>
+          <t>58,84; 72,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,39; 74,18</t>
+          <t>61,46; 75,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>62,89; 77,86</t>
+          <t>63,56; 78,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68,33; 78,04</t>
+          <t>68,9; 78,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64,66; 73,32</t>
+          <t>64,4; 73,06</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65,85; 75,04</t>
+          <t>66,18; 74,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>64,76; 75,03</t>
+          <t>64,66; 75,63</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,41; 86,47</t>
+          <t>70,68; 85,81</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>63,97; 83,05</t>
+          <t>62,64; 82,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61,3; 80,69</t>
+          <t>61,8; 81,17</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>65,23; 82,0</t>
+          <t>64,88; 82,57</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>61,32; 78,27</t>
+          <t>60,97; 78,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,65; 88,57</t>
+          <t>73,3; 87,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,77; 73,24</t>
+          <t>52,88; 72,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>55,85; 76,17</t>
+          <t>56,12; 76,67</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68,43; 80,16</t>
+          <t>68,76; 80,59</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72,08; 83,54</t>
+          <t>72,05; 83,85</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>60,7; 74,01</t>
+          <t>59,97; 74,02</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63,64; 77,04</t>
+          <t>63,28; 76,3</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>71,1; 76,68</t>
+          <t>70,94; 76,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69,45; 74,99</t>
+          <t>69,17; 74,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65,36; 71,51</t>
+          <t>65,73; 71,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67,72; 75,59</t>
+          <t>68,02; 75,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,41; 76,84</t>
+          <t>71,06; 76,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,77; 74,6</t>
+          <t>68,71; 74,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,36; 69,29</t>
+          <t>63,28; 68,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>66,6; 73,05</t>
+          <t>66,7; 72,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>71,97; 75,79</t>
+          <t>72,16; 75,84</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69,92; 73,75</t>
+          <t>69,9; 73,8</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65,04; 69,44</t>
+          <t>65,3; 69,65</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,02; 72,86</t>
+          <t>68,29; 73,39</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>72869; 86876</t>
+          <t>71829; 85804</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>62894; 76033</t>
+          <t>63458; 76431</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>38828; 53460</t>
+          <t>39346; 54249</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65613; 80367</t>
+          <t>65317; 80951</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>64600; 79145</t>
+          <t>65561; 79110</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>52907; 67473</t>
+          <t>53349; 68207</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>59468; 74586</t>
+          <t>60073; 74977</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>91069; 110957</t>
+          <t>90936; 109908</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>141944; 161931</t>
+          <t>141551; 160974</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>122661; 140332</t>
+          <t>121236; 140059</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103414; 124282</t>
+          <t>104171; 125333</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>162914; 186526</t>
+          <t>162471; 186174</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57976; 71121</t>
+          <t>57489; 70656</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>63378; 76850</t>
+          <t>62958; 77427</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>69915; 84185</t>
+          <t>70454; 84081</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60502; 74599</t>
+          <t>59641; 73910</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54935; 68234</t>
+          <t>54739; 68031</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>65272; 78905</t>
+          <t>64950; 79300</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65257; 81553</t>
+          <t>65273; 81439</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65962; 80159</t>
+          <t>65059; 79715</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>116760; 135568</t>
+          <t>117616; 135422</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133044; 152756</t>
+          <t>133947; 153561</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>139484; 160634</t>
+          <t>139886; 161305</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>130072; 149698</t>
+          <t>128948; 150165</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40610; 52763</t>
+          <t>40039; 52760</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>52505; 66051</t>
+          <t>52332; 66835</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35843; 47695</t>
+          <t>36415; 47229</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32119; 42632</t>
+          <t>31890; 42752</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>65988; 80391</t>
+          <t>66106; 79998</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>56420; 69282</t>
+          <t>55115; 68794</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43810; 56691</t>
+          <t>44006; 56562</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35540; 49132</t>
+          <t>35319; 48815</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>110456; 129781</t>
+          <t>111551; 129768</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>112364; 132248</t>
+          <t>113887; 132625</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>83862; 101589</t>
+          <t>85018; 101793</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>71626; 88883</t>
+          <t>69970; 88708</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>131300; 151578</t>
+          <t>131168; 151797</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>130035; 151482</t>
+          <t>129905; 151361</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>135670; 158607</t>
+          <t>136477; 158705</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>138932; 177247</t>
+          <t>138432; 176176</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>142095; 162203</t>
+          <t>142405; 160850</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>147287; 171914</t>
+          <t>147590; 170976</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>121873; 144844</t>
+          <t>122002; 145102</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>127373; 155457</t>
+          <t>128429; 156425</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>280199; 308500</t>
+          <t>278707; 308361</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>284572; 316139</t>
+          <t>285056; 315614</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>264364; 295572</t>
+          <t>263283; 295149</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>275631; 324848</t>
+          <t>274330; 324000</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>66823; 80915</t>
+          <t>67028; 81211</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96781; 115484</t>
+          <t>96797; 115037</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91221; 107372</t>
+          <t>90509; 107545</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71024; 89730</t>
+          <t>71213; 89659</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>86618; 102390</t>
+          <t>87020; 102025</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83578; 101715</t>
+          <t>83002; 102462</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87845; 106149</t>
+          <t>87939; 107601</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>102272; 126619</t>
+          <t>103364; 127696</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>156785; 179049</t>
+          <t>158071; 179359</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>187659; 212802</t>
+          <t>186902; 212045</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>183449; 209062</t>
+          <t>184369; 208018</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>181298; 210067</t>
+          <t>181015; 211730</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52918; 64078</t>
+          <t>52373; 63584</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>34484; 44772</t>
+          <t>33769; 44545</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37444; 49290</t>
+          <t>37755; 49586</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>44042; 55365</t>
+          <t>43808; 55748</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44387; 56659</t>
+          <t>44138; 57057</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54527; 65579</t>
+          <t>54270; 65061</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>36471; 49673</t>
+          <t>35867; 49238</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>40210; 54847</t>
+          <t>40409; 55205</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>100238; 117425</t>
+          <t>100731; 118057</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>92226; 106883</t>
+          <t>92185; 107281</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>78250; 95412</t>
+          <t>77307; 95423</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>88794; 107488</t>
+          <t>88296; 106454</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>450372; 485710</t>
+          <t>449371; 482974</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>470260; 507746</t>
+          <t>468351; 506280</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>435548; 476522</t>
+          <t>438022; 477963</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>441280; 492589</t>
+          <t>443270; 493592</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>486578; 523604</t>
+          <t>484223; 521804</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>491903; 533598</t>
+          <t>491489; 530364</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>445535; 487235</t>
+          <t>444923; 485087</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>497648; 545864</t>
+          <t>498408; 545413</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>946327; 996460</t>
+          <t>948784; 997198</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>973533; 1026898</t>
+          <t>973260; 1027512</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>890706; 951022</t>
+          <t>894230; 953874</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>951507; 1019196</t>
+          <t>955336; 1026684</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IQ23_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>74,58%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>68,07%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>67,72%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>75,51%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>76,55%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>78,3%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>57,25%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71,04%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>74,58%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>68,07%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>67,72%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>69,13; 82,58</t>
+          <t>67,1; 81,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,56; 84,99</t>
+          <t>58,85; 75,87</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>48,08; 66,3</t>
+          <t>60,1; 74,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62,96; 78,03</t>
+          <t>67,77; 81,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>67,21; 81,1</t>
+          <t>69,58; 82,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,43; 75,99</t>
+          <t>70,86; 84,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>60,2; 75,13</t>
+          <t>48,51; 65,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>67,21; 81,23</t>
+          <t>63,4; 77,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>70,27; 79,91</t>
+          <t>70,75; 80,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67,47; 77,94</t>
+          <t>67,84; 77,98</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>57,36; 69,01</t>
+          <t>56,61; 68,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,97; 77,88</t>
+          <t>68,67; 78,17</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>72,66%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75,36%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>66,49%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>77,39%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>75,08%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>75,6%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>73,82%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>71,26%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>72,66%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>75,36%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>66,49%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>76,38%</t>
+          <t>71,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,57%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,37; 81,57</t>
+          <t>63,93; 79,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,5; 83,02</t>
+          <t>67,15; 81,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,37; 80,4</t>
+          <t>58,68; 73,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62,99; 78,06</t>
+          <t>68,65; 83,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,56; 80,23</t>
+          <t>67,49; 81,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>67,11; 81,94</t>
+          <t>67,58; 82,49</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>58,88; 73,46</t>
+          <t>65,93; 80,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>68,07; 83,41</t>
+          <t>64,37; 79,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68,62; 79,0</t>
+          <t>68,31; 78,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>70,48; 80,8</t>
+          <t>70,56; 80,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,93; 74,87</t>
+          <t>64,52; 75,29</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>67,78; 78,93</t>
+          <t>68,84; 79,11</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>74,57%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>73,07%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>69,61%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>68,38%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>69,97%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>69,81%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>67,88%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>73,15%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>74,57%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,07%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,61%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>71,7%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59,41; 78,29</t>
+          <t>67,7; 81,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,74; 77,57</t>
+          <t>64,36; 80,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>58,89; 76,37</t>
+          <t>59,79; 77,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61,49; 82,44</t>
+          <t>58,17; 77,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>67,01; 81,1</t>
+          <t>60,48; 78,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>63,92; 79,79</t>
+          <t>61,37; 77,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,28; 77,48</t>
+          <t>57,81; 76,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>55,31; 76,45</t>
+          <t>63,72; 84,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>67,18; 78,16</t>
+          <t>66,88; 77,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66,07; 76,94</t>
+          <t>65,83; 76,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63,05; 75,49</t>
+          <t>62,11; 75,0</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60,47; 76,66</t>
+          <t>64,69; 78,5</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>75,27%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>70,26%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>64,09%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>66,24%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>71,7%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>69,05%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>66,63%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>71,22%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>75,27%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>70,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>64,09%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>66,7%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,27; 76,7</t>
+          <t>70,32; 79,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,48; 73,96</t>
+          <t>65,11; 75,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,6; 71,64</t>
+          <t>58,89; 69,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63,94; 81,37</t>
+          <t>59,49; 72,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,47; 79,6</t>
+          <t>66,15; 76,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,89; 75,17</t>
+          <t>63,48; 74,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,5; 69,57</t>
+          <t>61,27; 71,59</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,95; 71,8</t>
+          <t>61,62; 72,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69,68; 77,09</t>
+          <t>69,76; 77,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65,97; 73,04</t>
+          <t>65,56; 72,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61,21; 68,62</t>
+          <t>61,65; 69,31</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,15; 74,59</t>
+          <t>61,58; 70,72</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>75,19%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>66,39%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>68,2%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>72,17%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>71,85%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>71,5%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>73,19%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>69,42%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>75,19%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>66,39%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>68,2%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>64,76; 78,46</t>
+          <t>69,02; 80,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>64,89; 77,12</t>
+          <t>58,34; 72,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66,79; 79,37</t>
+          <t>61,73; 74,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>60,69; 76,41</t>
+          <t>64,35; 78,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>69,1; 81,02</t>
+          <t>64,72; 78,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,84; 72,64</t>
+          <t>64,83; 77,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,46; 75,2</t>
+          <t>66,56; 78,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>63,56; 78,53</t>
+          <t>65,21; 78,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>68,9; 78,17</t>
+          <t>68,45; 77,51</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64,4; 73,06</t>
+          <t>64,33; 73,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66,18; 74,67</t>
+          <t>66,02; 74,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>64,66; 75,63</t>
+          <t>66,88; 77,34</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>69,97%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81,52%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>63,4%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>68,43%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>79,19%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>73,78%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>71,91%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>74,17%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>69,97%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>81,52%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,4%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>74,93%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>71,7%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>70,68; 85,81</t>
+          <t>60,25; 77,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62,64; 82,63</t>
+          <t>73,77; 88,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61,8; 81,17</t>
+          <t>53,17; 72,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64,88; 82,57</t>
+          <t>57,67; 76,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>60,97; 78,82</t>
+          <t>70,56; 86,15</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,3; 87,88</t>
+          <t>63,35; 83,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52,88; 72,6</t>
+          <t>61,63; 80,58</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>56,12; 76,67</t>
+          <t>64,27; 82,43</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>68,76; 80,59</t>
+          <t>69,31; 80,17</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72,05; 83,85</t>
+          <t>72,05; 83,65</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>59,97; 74,02</t>
+          <t>60,43; 73,57</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>63,28; 76,3</t>
+          <t>65,82; 77,78</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>74,17%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>71,42%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>66,33%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>71,03%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>73,67%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>72,2%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>68,54%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>71,33%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>74,17%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>71,42%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>66,33%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>71,09%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>70,94; 76,25</t>
+          <t>71,59; 77,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>69,17; 74,77</t>
+          <t>68,37; 73,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>65,73; 71,72</t>
+          <t>63,1; 69,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>68,02; 75,74</t>
+          <t>67,63; 74,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,06; 76,58</t>
+          <t>70,76; 76,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,71; 74,15</t>
+          <t>69,44; 74,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,28; 68,99</t>
+          <t>65,45; 71,31</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>66,7; 72,99</t>
+          <t>68,0; 74,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>72,16; 75,84</t>
+          <t>72,03; 75,77</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>69,9; 73,8</t>
+          <t>69,71; 74,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>65,3; 69,65</t>
+          <t>65,29; 69,55</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>68,29; 73,39</t>
+          <t>68,96; 73,57</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>71</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>106</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>72752</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>61106</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>67584</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>91342</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>79537</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>70419</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>46845</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>73700</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>72752</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>61106</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>67584</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>101442</t>
+          <t>72851</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>175143</t>
+          <t>164193</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>71829; 85804</t>
+          <t>65451; 79314</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>63458; 76431</t>
+          <t>52827; 68103</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>39346; 54249</t>
+          <t>59977; 74737</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>65317; 80951</t>
+          <t>81980; 98150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>65561; 79110</t>
+          <t>72297; 86188</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>53349; 68207</t>
+          <t>63727; 76008</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>60073; 74977</t>
+          <t>39695; 53766</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>90936; 109908</t>
+          <t>64773; 79641</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>141551; 160974</t>
+          <t>142527; 161749</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>121236; 140059</t>
+          <t>121903; 140130</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>104171; 125333</t>
+          <t>102815; 124369</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>162471; 186174</t>
+          <t>153215; 174430</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>98</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>61610</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72933</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>73714</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>70734</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>65030</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>70506</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>77200</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>67473</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>61610</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72933</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>73714</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>72994</t>
+          <t>69416</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>140468</t>
+          <t>140150</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57489; 70656</t>
+          <t>54207; 67527</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>62958; 77427</t>
+          <t>64986; 79119</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>70454; 84081</t>
+          <t>65056; 81359</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59641; 73910</t>
+          <t>62740; 76326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>54739; 68031</t>
+          <t>58461; 70791</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>64950; 79300</t>
+          <t>63025; 76937</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65273; 81439</t>
+          <t>68945; 84456</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>65059; 79715</t>
+          <t>62145; 76858</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>117616; 135422</t>
+          <t>117098; 134969</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133947; 153561</t>
+          <t>134103; 152498</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>139886; 161305</t>
+          <t>139007; 162202</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>128948; 150165</t>
+          <t>129382; 148684</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>64</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>73563</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>63004</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>50815</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>38938</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>47152</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>60146</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>41978</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>37934</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>73563</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>63004</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>50815</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>42846</t>
+          <t>40230</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>80780</t>
+          <t>79168</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>40039; 52760</t>
+          <t>66786; 80105</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>52332; 66835</t>
+          <t>55494; 69348</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36415; 47229</t>
+          <t>43649; 56770</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31890; 42752</t>
+          <t>33122; 44218</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>66106; 79998</t>
+          <t>40760; 52857</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55115; 68794</t>
+          <t>52872; 66844</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44006; 56562</t>
+          <t>35749; 47440</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35319; 48815</t>
+          <t>34080; 44968</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>111551; 129768</t>
+          <t>111041; 129039</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>113887; 132625</t>
+          <t>113477; 132135</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85018; 101793</t>
+          <t>83751; 101134</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>69970; 88708</t>
+          <t>71428; 86686</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>203</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>223</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>177</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>152091</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>159805</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>133663</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>133574</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>141910</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>141316</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>147620</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>154205</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>152091</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>159805</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>133663</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>142094</t>
+          <t>119160</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>296299</t>
+          <t>252733</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>131168; 151797</t>
+          <t>142091; 160941</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>129905; 151361</t>
+          <t>148079; 171100</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136477; 158705</t>
+          <t>122819; 144528</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>138432; 176176</t>
+          <t>119956; 145724</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>142405; 160850</t>
+          <t>130914; 151455</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>147590; 170976</t>
+          <t>129909; 151944</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>122002; 145102</t>
+          <t>135749; 158596</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>128429; 156425</t>
+          <t>109228; 129301</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>278707; 308361</t>
+          <t>279028; 308210</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>285056; 315614</t>
+          <t>283288; 315266</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>263283; 295149</t>
+          <t>265175; 298099</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>274330; 324000</t>
+          <t>233339; 267961</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>149</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>123</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>133</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>94688</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>93649</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>97581</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>106982</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>74371</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>106658</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>99183</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>81460</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>94688</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>93649</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97581</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>114445</t>
+          <t>84329</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>195906</t>
+          <t>191312</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>67028; 81211</t>
+          <t>86922; 101530</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>96797; 115037</t>
+          <t>82300; 101941</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90509; 107545</t>
+          <t>88331; 106516</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>71213; 89659</t>
+          <t>95389; 116779</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>87020; 102025</t>
+          <t>66986; 81449</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>83002; 102462</t>
+          <t>96706; 115129</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>87939; 107601</t>
+          <t>90187; 106913</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>103364; 127696</t>
+          <t>76105; 91335</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>158071; 179359</t>
+          <t>157059; 177834</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>186902; 212045</t>
+          <t>186711; 212801</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>184369; 208018</t>
+          <t>183917; 208917</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>181015; 211730</t>
+          <t>177216; 204918</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>56</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>67</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>50652</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>60358</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>42999</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>46732</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>58683</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>39776</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>43927</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>50081</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>50652</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>60358</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>42999</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>48118</t>
+          <t>51883</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>98199</t>
+          <t>98616</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>52373; 63584</t>
+          <t>43615; 56167</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>33769; 44545</t>
+          <t>54617; 65311</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37755; 49586</t>
+          <t>36060; 48973</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>43808; 55748</t>
+          <t>39383; 52359</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>44138; 57057</t>
+          <t>52283; 63835</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>54270; 65061</t>
+          <t>34151; 44818</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>35867; 49238</t>
+          <t>37651; 49225</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>40409; 55205</t>
+          <t>44506; 57078</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>100731; 118057</t>
+          <t>101539; 117445</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>92185; 107281</t>
+          <t>92192; 107029</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>77307; 95423</t>
+          <t>77903; 94843</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>88296; 106454</t>
+          <t>90525; 106967</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>757</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>664</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>691</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>683</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>623</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>757</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>664</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>505358</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>510855</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>466358</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>488302</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>466684</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>488821</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>456753</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>464855</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>505358</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>510855</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>466358</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>521940</t>
+          <t>437870</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>986795</t>
+          <t>926172</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>449371; 482974</t>
+          <t>487777; 525687</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>468351; 506280</t>
+          <t>489022; 528612</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>438022; 477963</t>
+          <t>443686; 485496</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>443270; 493592</t>
+          <t>464917; 510948</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>484223; 521804</t>
+          <t>448196; 483652</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>491489; 530364</t>
+          <t>470158; 507207</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>444923; 485087</t>
+          <t>436163; 475225</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>498408; 545413</t>
+          <t>418464; 455842</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>948784; 997198</t>
+          <t>947021; 996256</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>973260; 1027512</t>
+          <t>970684; 1030661</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>894230; 953874</t>
+          <t>894194; 952468</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>955336; 1026684</t>
+          <t>898414; 958580</t>
         </is>
       </c>
     </row>
